--- a/p6_deployment/data/usa/missing/data_understanding/df_match_player_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1940 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>COgk2UVd</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>I5BDsX50</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lee jackson</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>r5zgq7ga</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>twumasi kofi</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SdGJHbfQ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>yao karifa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>fZOV3MQb</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nodarse frank</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pMiZqUWF</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>turnbull stephen</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ABgybAKc</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>holstad clay</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>fFGWyWGc</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>brito joe</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>GUL6UkS5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ybarra marc</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bPFJK7Aq</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>kwizera jojea</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>djBFSyEl</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>dikwa albert</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>CzZq1qid</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>williams jj</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dOxI9MKG</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>pasquel ramon</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2JN1MDYl</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>lyons miles</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>bmja4NbJ</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>craig brandan</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>61u8Ap9R</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>dollenmayer noah</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>pY0wQDfp</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>borelli eder</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2aWqq3yE</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>calvillo eric</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>2Lu27gga</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>akinyode bolu</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>GYF2Siak</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>zacarias ricardo</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>IVAH3POn</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>nevarez francisco</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>40hYTKFF</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>moshobane tumi</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>61YPh7Nh</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>garay jeremy</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>QLwBlkVS</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>angking isaac</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>pCy6heIQ</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>doyle mark</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vaN7FIP6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>fuson noah</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>YguzBHPo</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>koke vegas</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>SKDsui3p</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>mcglynn conor</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>p4My3U8s</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>orduy kevin</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Auz4PTZ3</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>smith collin</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>S4F7Co96</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>vang kevin</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>lCUVNwwn</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>dhillon justin</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>OKIXsIIl</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>garcia javier</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>Ummi57wm</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>hinds nick</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>pASl4ZnA</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>moreno amando</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>vR4farZA</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>petrovic petar</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>Kfa88uP3</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>rivas joaquin</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>nuON8BH2</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>yuma</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>SKDsui3p</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>mcglynn conor</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>SKDsui3p</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>mcglynn conor</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>r5zgq7ga</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>twumasi kofi</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>QLwBlkVS</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>angking isaac</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>QLwBlkVS</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>angking isaac</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>fFGWyWGc</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>brito joe</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>Auz4PTZ3</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>smith collin</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>Auz4PTZ3</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>smith collin</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>pMiZqUWF</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>turnbull stephen</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>vaN7FIP6</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>fuson noah</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>vaN7FIP6</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>fuson noah</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>bPFJK7Aq</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>kwizera jojea</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>pASl4ZnA</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>moreno amando</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>pASl4ZnA</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>moreno amando</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>61YPh7Nh</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>garay jeremy</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>lCUVNwwn</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>dhillon justin</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>lCUVNwwn</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>dhillon justin</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>GYF2Siak</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>zacarias ricardo</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>vR4farZA</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>petrovic petar</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>vR4farZA</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>petrovic petar</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>2Lu27gga</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>akinyode bolu</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Kfa88uP3</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>rivas joaquin</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Kfa88uP3</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>rivas joaquin</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>40hYTKFF</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>moshobane tumi</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Ummi57wm</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>hinds nick</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Ummi57wm</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>hinds nick</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>pY0wQDfp</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>borelli eder</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>bL57wogd</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>67li1ynd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>saldana carlos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AitxpHkS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sheldon matthew</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4zLmP9V3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>carroll stephen</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>lErgyewE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>amoo mensah devon</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Gz4oOThB</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>levis brett</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>IRtMcckd</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>williams rhys</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>hrfUopwP</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>murphy james</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>vVJtIvTu</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>abdoulaye diop</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>td2rqnzC</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>morris ben</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>zRXV8mvM</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>rodriguez maxi</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>C46Ufw7d</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>amoh elvis</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>YVRXszaF</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>hibbert jayden</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>O8S4A8iq</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dodson derek</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>WjEIUyMQ</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>crognale alex</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>hv6lPAU9</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>kavita phanuel</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2ZC96wer</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>paterson aj</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>noFkUkB1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>tabortetaka preston</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Emuusx6F</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>hernandez foster kobe</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>W0IPa6za</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>perez miguel</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>hhqa8nNc</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>kassim prosper</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>OYA19zBf</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>martinez enzo</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>6Dhlor2O</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>pasher tyler</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>ATW1gdHm</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>bezerra victor</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Cn8rU1bf</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>gasso dominic</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2XXjV3ia</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>matthews yazeed</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>ENKoHGRC</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>salim abdi</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>vs4ZkyjL</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>steinwascher nathan</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>847Q5dgk</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>williams ryan</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>dbxK7ytt</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>calloway finn</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>vZe9Zyx8</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>hamouda ramiz</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>fgUneYj4</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>jack owen</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>2sG4esMB</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>mensah moses</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>fymCnmrE</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>nwegbo diba</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>Gz4oOThB</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>levis brett</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>847Q5dgk</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>williams ryan</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>847Q5dgk</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>williams ryan</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>IRtMcckd</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>williams rhys</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>2XXjV3ia</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>matthews yazeed</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>2XXjV3ia</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>matthews yazeed</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>C46Ufw7d</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>amoh elvis</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>ENKoHGRC</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>salim abdi</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>ENKoHGRC</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>salim abdi</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>GQtRHQGM</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>villanueva alex</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>2sG4esMB</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>mensah moses</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>2sG4esMB</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>mensah moses</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>W0IPa6za</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>perez miguel</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>fymCnmrE</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>nwegbo diba</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>fymCnmrE</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>nwegbo diba</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>hhqa8nNc</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>kassim prosper</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>vZe9Zyx8</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>hamouda ramiz</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>vZe9Zyx8</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>hamouda ramiz</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>noFkUkB1</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>tabortetaka preston</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>Cn8rU1bf</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>gasso dominic</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>Cn8rU1bf</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>gasso dominic</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>hrfUopwP</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>murphy james</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>